--- a/output/Gym_Elektrik_BoQ.xlsx
+++ b/output/Gym_Elektrik_BoQ.xlsx
@@ -1544,7 +1544,7 @@
         </is>
       </c>
       <c r="E18" s="21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F18" s="22" t="n"/>
       <c r="G18" s="23">
@@ -1552,10 +1552,10 @@
         <v/>
       </c>
       <c r="H18" s="24" t="n">
-        <v>13640</v>
+        <v>12400</v>
       </c>
       <c r="I18" s="24" t="n">
-        <v>23100</v>
+        <v>21000</v>
       </c>
     </row>
     <row r="19">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>Su ısıtıcı besleme hattı 3×4 mm² + 32 A kesici</t>
+          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -1696,10 +1696,10 @@
         <v/>
       </c>
       <c r="H22" s="24" t="n">
-        <v>10400</v>
+        <v>12800</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>17600</v>
+        <v>21600</v>
       </c>
     </row>
     <row r="23">
@@ -2622,7 +2622,7 @@
         </is>
       </c>
       <c r="B22" s="37" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
@@ -3144,7 +3144,7 @@
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
-          <t>1×32 A · 3×4 mm²</t>
+          <t>1×32 A · 3×6 mm²</t>
         </is>
       </c>
       <c r="D51" s="44" t="inlineStr">
@@ -3166,7 +3166,7 @@
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>1×32 A · 3×4 mm²</t>
+          <t>1×32 A · 3×6 mm²</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">

--- a/output/Gym_Elektrik_BoQ.xlsx
+++ b/output/Gym_Elektrik_BoQ.xlsx
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev C · 13 Eylül 2026 · Eylül 2026 piyasa mertebesi · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev E · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev C · 13 Eylül 2026 · Fiyat referansı: Eylül 2026 piyasa mertebesi · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Elektrik_BoQ.xlsx
+++ b/output/Gym_Elektrik_BoQ.xlsx
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev E · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev F · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev E · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev F · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
         </is>
       </c>
       <c r="E7" s="29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="F7" s="22" t="n"/>
       <c r="G7" s="30">
@@ -1156,10 +1156,10 @@
         <v/>
       </c>
       <c r="H7" s="31" t="n">
-        <v>13020</v>
+        <v>13640</v>
       </c>
       <c r="I7" s="31" t="n">
-        <v>22050</v>
+        <v>23100</v>
       </c>
     </row>
     <row r="8">
@@ -1436,7 +1436,7 @@
         </is>
       </c>
       <c r="E15" s="29" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="F15" s="22" t="n"/>
       <c r="G15" s="30">
@@ -1444,10 +1444,10 @@
         <v/>
       </c>
       <c r="H15" s="31" t="n">
-        <v>18920</v>
+        <v>4620</v>
       </c>
       <c r="I15" s="31" t="n">
-        <v>31820</v>
+        <v>7770</v>
       </c>
     </row>
     <row r="16">
@@ -1616,7 +1616,7 @@
         </is>
       </c>
       <c r="E20" s="21" t="n">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="F20" s="22" t="n"/>
       <c r="G20" s="23">
@@ -1624,10 +1624,10 @@
         <v/>
       </c>
       <c r="H20" s="24" t="n">
-        <v>27020</v>
+        <v>54740</v>
       </c>
       <c r="I20" s="24" t="n">
-        <v>44390</v>
+        <v>89930</v>
       </c>
     </row>
     <row r="21">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>Su ısıtıcı besleme hattı 3×6 mm² + 32 A kesici + 30 mA kaçak akım</t>
+          <t>Boyler besleme hattı 3×2,5 mm² + 20 A kesici + 30 mA kaçak akım</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -1696,10 +1696,10 @@
         <v/>
       </c>
       <c r="H22" s="24" t="n">
-        <v>12800</v>
+        <v>8400</v>
       </c>
       <c r="I22" s="24" t="n">
-        <v>21600</v>
+        <v>14600</v>
       </c>
     </row>
     <row r="23">
@@ -2354,7 +2354,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D56"/>
+  <dimension ref="A1:D57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -2394,7 +2394,7 @@
         </is>
       </c>
       <c r="B5" s="35" t="n">
-        <v>26.59</v>
+        <v>20.59</v>
       </c>
       <c r="C5" s="7" t="inlineStr">
         <is>
@@ -2410,7 +2410,7 @@
         </is>
       </c>
       <c r="B6" s="37" t="n">
-        <v>17.03</v>
+        <v>14.63</v>
       </c>
       <c r="C6" s="11" t="inlineStr">
         <is>
@@ -2426,7 +2426,7 @@
         </is>
       </c>
       <c r="B7" s="35" t="n">
-        <v>0.2</v>
+        <v>1</v>
       </c>
       <c r="C7" s="7" t="inlineStr">
         <is>
@@ -2458,7 +2458,7 @@
         </is>
       </c>
       <c r="B9" s="35" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C9" s="7" t="inlineStr">
         <is>
@@ -2484,7 +2484,7 @@
         </is>
       </c>
       <c r="B12" s="37" t="n">
-        <v>5.68</v>
+        <v>4.86</v>
       </c>
       <c r="C12" s="11" t="inlineStr">
         <is>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="B13" s="35" t="n">
-        <v>5.68</v>
+        <v>4.91</v>
       </c>
       <c r="C13" s="7" t="inlineStr">
         <is>
@@ -2516,7 +2516,7 @@
         </is>
       </c>
       <c r="B14" s="37" t="n">
-        <v>5.67</v>
+        <v>4.87</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
@@ -2532,7 +2532,7 @@
         </is>
       </c>
       <c r="B15" s="35" t="n">
-        <v>26.8</v>
+        <v>23</v>
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="B16" s="37" t="n">
-        <v>26.8</v>
+        <v>23.2</v>
       </c>
       <c r="C16" s="11" t="inlineStr">
         <is>
@@ -2564,7 +2564,7 @@
         </is>
       </c>
       <c r="B17" s="35" t="n">
-        <v>26.8</v>
+        <v>23</v>
       </c>
       <c r="C17" s="7" t="inlineStr">
         <is>
@@ -2712,7 +2712,7 @@
         </is>
       </c>
       <c r="B29" s="35" t="n">
-        <v>172</v>
+        <v>42</v>
       </c>
       <c r="C29" s="7" t="inlineStr">
         <is>
@@ -2728,7 +2728,7 @@
         </is>
       </c>
       <c r="B30" s="37" t="n">
-        <v>193</v>
+        <v>391</v>
       </c>
       <c r="C30" s="11" t="inlineStr">
         <is>
@@ -2814,12 +2814,12 @@
       </c>
       <c r="C36" s="41" t="inlineStr">
         <is>
-          <t>1×10 A · 3×1,5 mm²</t>
+          <t>1×10 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D36" s="41" t="inlineStr">
         <is>
-          <t>L3 · 0.28 · 0.28</t>
+          <t>L2 · 0.28 · 0.28</t>
         </is>
       </c>
     </row>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="C37" s="44" t="inlineStr">
         <is>
-          <t>1×10 A · 3×1,5 mm²</t>
+          <t>1×10 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D37" s="44" t="inlineStr">
@@ -2858,7 +2858,7 @@
       </c>
       <c r="C38" s="41" t="inlineStr">
         <is>
-          <t>1×10 A · 3×1,5 mm²</t>
+          <t>1×10 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D38" s="41" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="C39" s="44" t="inlineStr">
         <is>
-          <t>1×10 A · 3×1,5 mm²</t>
+          <t>1×10 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D39" s="44" t="inlineStr">
@@ -2902,12 +2902,12 @@
       </c>
       <c r="C40" s="41" t="inlineStr">
         <is>
-          <t>1×10 A · 3×1,5 mm²</t>
+          <t>1×10 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D40" s="41" t="inlineStr">
         <is>
-          <t>L2 · 0.11 · 0.07</t>
+          <t>L1 · 0.11 · 0.07</t>
         </is>
       </c>
     </row>
@@ -2924,12 +2924,12 @@
       </c>
       <c r="C41" s="44" t="inlineStr">
         <is>
-          <t>1×6 A · 3×1,5 mm²</t>
+          <t>1×6 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D41" s="44" t="inlineStr">
         <is>
-          <t>L1 · 0.06 · 0.06</t>
+          <t>L2 · 0.06 · 0.06</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2941,7 @@
       </c>
       <c r="B42" s="40" t="inlineStr">
         <is>
-          <t>Priz — salon kuzey ve batı</t>
+          <t>Priz — salon kuzey (PR12–PR16, PR1)</t>
         </is>
       </c>
       <c r="C42" s="41" t="inlineStr">
@@ -2951,7 +2951,7 @@
       </c>
       <c r="D42" s="41" t="inlineStr">
         <is>
-          <t>L1 · 1.20 · 0.60</t>
+          <t>L1 · 0.90 · 0.45</t>
         </is>
       </c>
     </row>
@@ -2963,7 +2963,7 @@
       </c>
       <c r="B43" s="43" t="inlineStr">
         <is>
-          <t>Priz — salon güney ve doğu</t>
+          <t>Priz — salon güney (PR5–PR9)</t>
         </is>
       </c>
       <c r="C43" s="44" t="inlineStr">
@@ -2973,19 +2973,19 @@
       </c>
       <c r="D43" s="44" t="inlineStr">
         <is>
-          <t>L3 · 1.20 · 0.60</t>
+          <t>L3 · 0.75 · 0.38</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="39" t="inlineStr">
         <is>
-          <t>P3</t>
+          <t>P6</t>
         </is>
       </c>
       <c r="B44" s="40" t="inlineStr">
         <is>
-          <t>Priz — banko, POS, veri</t>
+          <t>Priz — salon batı ve doğu (PR2–PR4, PR10, PR11)</t>
         </is>
       </c>
       <c r="C44" s="41" t="inlineStr">
@@ -2995,19 +2995,19 @@
       </c>
       <c r="D44" s="41" t="inlineStr">
         <is>
-          <t>L2 · 1.00 · 0.70</t>
+          <t>L1 · 0.75 · 0.38</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="42" t="inlineStr">
         <is>
-          <t>P4</t>
+          <t>P3</t>
         </is>
       </c>
       <c r="B45" s="43" t="inlineStr">
         <is>
-          <t>Priz — kardiyo ekipmanı (ayrı linye)</t>
+          <t>Priz — banko, POS, veri</t>
         </is>
       </c>
       <c r="C45" s="44" t="inlineStr">
@@ -3017,19 +3017,19 @@
       </c>
       <c r="D45" s="44" t="inlineStr">
         <is>
-          <t>L3 · 2.40 · 1.92</t>
+          <t>L2 · 1.00 · 0.70</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="39" t="inlineStr">
         <is>
-          <t>P5</t>
+          <t>P4</t>
         </is>
       </c>
       <c r="B46" s="40" t="inlineStr">
         <is>
-          <t>Priz — ıslak hacim IP44 (ayrı kaçak akım)</t>
+          <t>Priz — kardiyo ekipmanı (ayrı linye)</t>
         </is>
       </c>
       <c r="C46" s="41" t="inlineStr">
@@ -3039,19 +3039,19 @@
       </c>
       <c r="D46" s="41" t="inlineStr">
         <is>
-          <t>L2 · 0.50 · 0.15</t>
+          <t>L1 · 2.40 · 1.92</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="42" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>P5</t>
         </is>
       </c>
       <c r="B47" s="43" t="inlineStr">
         <is>
-          <t>Klima — arena 24.000 BTU</t>
+          <t>Priz — ıslak hacim IP44 (ayrı kaçak akım)</t>
         </is>
       </c>
       <c r="C47" s="44" t="inlineStr">
@@ -3061,19 +3061,19 @@
       </c>
       <c r="D47" s="44" t="inlineStr">
         <is>
-          <t>L3 · 2.20 · 1.87</t>
+          <t>L3 · 0.50 · 0.15</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="39" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="B48" s="40" t="inlineStr">
         <is>
-          <t>Klima — fonksiyonel 18.000 BTU</t>
+          <t>Klima — arena 24.000 BTU</t>
         </is>
       </c>
       <c r="C48" s="41" t="inlineStr">
@@ -3083,19 +3083,19 @@
       </c>
       <c r="D48" s="41" t="inlineStr">
         <is>
-          <t>L1 · 1.70 · 1.45</t>
+          <t>L2 · 2.20 · 1.87</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="42" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="B49" s="43" t="inlineStr">
         <is>
-          <t>Klima — giriş 12.000 BTU</t>
+          <t>Klima — fonksiyonel 18.000 BTU</t>
         </is>
       </c>
       <c r="C49" s="44" t="inlineStr">
@@ -3105,19 +3105,19 @@
       </c>
       <c r="D49" s="44" t="inlineStr">
         <is>
-          <t>L2 · 1.15 · 0.98</t>
+          <t>L2 · 1.70 · 1.45</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="39" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="B50" s="40" t="inlineStr">
         <is>
-          <t>Klima — dinlenme 12.000 BTU</t>
+          <t>Klima — giriş 12.000 BTU</t>
         </is>
       </c>
       <c r="C50" s="41" t="inlineStr">
@@ -3127,139 +3127,161 @@
       </c>
       <c r="D50" s="41" t="inlineStr">
         <is>
-          <t>L3 · 1.15 · 0.81</t>
+          <t>L1 · 1.15 · 0.98</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="42" t="inlineStr">
         <is>
-          <t>W1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="B51" s="43" t="inlineStr">
         <is>
-          <t>Su ısıtıcı — erkek bloğu 6 kW</t>
+          <t>Klima — dinlenme 12.000 BTU</t>
         </is>
       </c>
       <c r="C51" s="44" t="inlineStr">
         <is>
-          <t>1×32 A · 3×6 mm²</t>
+          <t>1×16 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D51" s="44" t="inlineStr">
         <is>
-          <t>L1 · 6.00 · 3.00</t>
+          <t>L1 · 1.15 · 0.81</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="39" t="inlineStr">
         <is>
-          <t>W2</t>
+          <t>W1</t>
         </is>
       </c>
       <c r="B52" s="40" t="inlineStr">
         <is>
-          <t>Su ısıtıcı — kadın bloğu 6 kW</t>
+          <t>Su ısıtıcı — erkek bloğu, boyler 3 kW</t>
         </is>
       </c>
       <c r="C52" s="41" t="inlineStr">
         <is>
-          <t>1×32 A · 3×6 mm²</t>
+          <t>1×20 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D52" s="41" t="inlineStr">
         <is>
-          <t>L2 · 6.00 · 3.00</t>
+          <t>L3 · 3.00 · 1.80</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="42" t="inlineStr">
         <is>
-          <t>V1</t>
+          <t>W2</t>
         </is>
       </c>
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>Havalandırma — taze hava + egzoz fanı</t>
+          <t>Su ısıtıcı — kadın bloğu, boyler 3 kW</t>
         </is>
       </c>
       <c r="C53" s="44" t="inlineStr">
         <is>
-          <t>1×10 A · 3×1,5 mm²</t>
+          <t>1×20 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D53" s="44" t="inlineStr">
         <is>
-          <t>L1 · 0.45 · 0.45</t>
+          <t>L3 · 3.00 · 1.80</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="39" t="inlineStr">
         <is>
-          <t>V2</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="B54" s="40" t="inlineStr">
         <is>
-          <t>Islak hacim egzoz fanı</t>
+          <t>Havalandırma — taze hava + egzoz fanı</t>
         </is>
       </c>
       <c r="C54" s="41" t="inlineStr">
         <is>
-          <t>1×6 A · 3×1,5 mm²</t>
+          <t>1×10 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D54" s="41" t="inlineStr">
         <is>
-          <t>L2 · 0.12 · 0.10</t>
+          <t>L2 · 0.45 · 0.45</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="42" t="inlineStr">
         <is>
-          <t>Z1</t>
+          <t>V2</t>
         </is>
       </c>
       <c r="B55" s="43" t="inlineStr">
         <is>
-          <t>Zayıf akım — rack, CCTV, ses, geçiş kontrol</t>
+          <t>Islak hacim egzoz fanı</t>
         </is>
       </c>
       <c r="C55" s="44" t="inlineStr">
         <is>
-          <t>1×10 A · 3×2,5 mm²</t>
+          <t>1×6 A · 3×2,5 mm²</t>
         </is>
       </c>
       <c r="D55" s="44" t="inlineStr">
         <is>
-          <t>L2 · 0.60 · 0.54</t>
+          <t>L2 · 0.12 · 0.10</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="39" t="inlineStr">
         <is>
+          <t>Z1</t>
+        </is>
+      </c>
+      <c r="B56" s="40" t="inlineStr">
+        <is>
+          <t>Zayıf akım — rack, CCTV, ses, geçiş kontrol</t>
+        </is>
+      </c>
+      <c r="C56" s="41" t="inlineStr">
+        <is>
+          <t>1×10 A · 3×2,5 mm²</t>
+        </is>
+      </c>
+      <c r="D56" s="41" t="inlineStr">
+        <is>
+          <t>L3 · 0.60 · 0.54</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="42" t="inlineStr">
+        <is>
           <t>Z2</t>
         </is>
       </c>
-      <c r="B56" s="40" t="inlineStr">
+      <c r="B57" s="43" t="inlineStr">
         <is>
           <t>Yangın algılama paneli (kesintisiz)</t>
         </is>
       </c>
-      <c r="C56" s="41" t="inlineStr">
-        <is>
-          <t>1×6 A · 3×1,5 mm²</t>
-        </is>
-      </c>
-      <c r="D56" s="41" t="inlineStr">
-        <is>
-          <t>L2 · 0.15 · 0.15</t>
+      <c r="C57" s="44" t="inlineStr">
+        <is>
+          <t>1×6 A · 3×2,5 mm²</t>
+        </is>
+      </c>
+      <c r="D57" s="44" t="inlineStr">
+        <is>
+          <t>L1 · 0.15 · 0.15</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Elektrik_BoQ.xlsx
+++ b/output/Gym_Elektrik_BoQ.xlsx
@@ -712,7 +712,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Rev G · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
+          <t>Rev H · 17 Eylül 2026 · Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Ekipman işverence temin edilmiştir, bütçe dışıdır.</t>
         </is>
       </c>
     </row>
@@ -967,7 +967,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev G · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
+          <t>MALTEPE / İDEALTEPE — MOBİLYA MAĞAZASI → FONKSİYONEL ANTRENMAN STÜDYOSU · Rev H · 17 Eylül 2026 · Fiyat referansı: Eylül 2026 · Aqua Florya / Saltbae kesin hakedişi (Mayıs 2025) birim fiyatları ×1,40 eskalasyonla · Birim fiyat sütununu (F) doldurun, tutarlar kendiliğinden hesaplanır</t>
         </is>
       </c>
     </row>

--- a/output/Gym_Elektrik_BoQ.xlsx
+++ b/output/Gym_Elektrik_BoQ.xlsx
@@ -2156,7 +2156,7 @@
         </is>
       </c>
       <c r="E35" s="29" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F35" s="22" t="n"/>
       <c r="G35" s="30">
@@ -2164,10 +2164,10 @@
         <v/>
       </c>
       <c r="H35" s="31" t="n">
-        <v>12600</v>
+        <v>12720</v>
       </c>
       <c r="I35" s="31" t="n">
-        <v>22050</v>
+        <v>22260</v>
       </c>
     </row>
     <row r="36">
@@ -2744,7 +2744,7 @@
         </is>
       </c>
       <c r="B31" s="35" t="n">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="C31" s="7" t="inlineStr">
         <is>
